--- a/erp-server/erp-server-file/src/main/resources/excel/wms/firstMileProcessing.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/firstMileProcessing.xlsx
@@ -73,19 +73,19 @@
     <t>{.requisitionApplicationCode}</t>
   </si>
   <si>
-    <t>{.soApproveStatusName}</t>
+    <t>{.requisitionApplicationStatusName}</t>
   </si>
   <si>
     <t>{.approveQty}</t>
   </si>
   <si>
-    <t>{.firstMileDeliveryCode}</t>
-  </si>
-  <si>
-    <t>{.deliveryApproveStatusName}</t>
-  </si>
-  <si>
-    <t>{.deliveryQty}</t>
+    <t>{.firstMileDeliveryCodes}</t>
+  </si>
+  <si>
+    <t>{.deliveryApproveStatusNames}</t>
+  </si>
+  <si>
+    <t>{.deliveryQtySum}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -100,7 +100,7 @@
     <t>{.frozenTime}</t>
   </si>
   <si>
-    <t>{.outstockQty}</t>
+    <t>{.outstockQtySum}</t>
   </si>
   <si>
     <t>{.frozenQty}</t>
@@ -1041,7 +1041,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
-    <col min="2" max="2" width="16.875" customWidth="1"/>
+    <col min="2" max="2" width="23.5" customWidth="1"/>
     <col min="3" max="4" width="16.125" customWidth="1"/>
     <col min="5" max="5" width="15.875" customWidth="1"/>
     <col min="6" max="6" width="14.875" customWidth="1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/firstMileProcessing.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/firstMileProcessing.xlsx
@@ -79,13 +79,13 @@
     <t>{.approveQty}</t>
   </si>
   <si>
-    <t>{.firstMileDeliveryCodes}</t>
-  </si>
-  <si>
-    <t>{.deliveryApproveStatusNames}</t>
-  </si>
-  <si>
-    <t>{.deliveryQtySum}</t>
+    <t>{.firstMileDeliveryCode}</t>
+  </si>
+  <si>
+    <t>{.deliveryApproveStatusName}</t>
+  </si>
+  <si>
+    <t>{.deliveryQty}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -100,7 +100,7 @@
     <t>{.frozenTime}</t>
   </si>
   <si>
-    <t>{.outstockQtySum}</t>
+    <t>{.outstockQty}</t>
   </si>
   <si>
     <t>{.frozenQty}</t>
